--- a/apps/desktop/public/mau-nhap-nhan-vien.xlsx
+++ b/apps/desktop/public/mau-nhap-nhan-vien.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nhân viên" sheetId="1" r:id="Re3ebd890c6274042"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hướng dẫn" sheetId="2" r:id="Rfe2130a2ddd84074"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nhân viên" sheetId="1" r:id="R725cb7483d554bc6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hướng dẫn" sheetId="2" r:id="R9aeb9147125443ac"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -254,7 +254,7 @@
   <x:dxfs count="1">
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF7FAFD"/>
         </x:patternFill>
       </x:fill>
@@ -484,7 +484,7 @@
     </x:row>
     <x:row r="2" ht="31" customHeight="1">
       <x:c r="A2" s="9" t="str">
-        <x:v>Giữ nguyên tên cột. CCCD là chuỗi 9–12 chữ số. Ngày sinh dùng định dạng dd/mm/yyyy. Có thể xóa các dòng minh họa trước khi nhập.</x:v>
+        <x:v>Giữ nguyên tên cột. CCCD bắt buộc đúng 12 chữ số và được giữ dạng text. Ngày sinh dùng định dạng dd/mm/yyyy. Có thể xóa các dòng minh họa trước khi nhập.</x:v>
       </x:c>
       <x:c r="B2" s="9"/>
       <x:c r="C2" s="9"/>
@@ -11631,7 +11631,7 @@
         <x:v>CCCD</x:v>
       </x:c>
       <x:c r="B4" s="42" t="str">
-        <x:v>Bắt buộc; 9–12 chữ số; luôn được giữ dạng chuỗi; dùng để phát hiện hồ sơ trùng.</x:v>
+        <x:v>Bắt buộc; đúng 12 chữ số; luôn được giữ dạng text; dùng để phát hiện hồ sơ trùng.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
